--- a/artfynd/A 31018-2023 artfynd.xlsx
+++ b/artfynd/A 31018-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31018-2023 artfynd.xlsx
+++ b/artfynd/A 31018-2023 artfynd.xlsx
@@ -9688,7 +9688,7 @@
         <v>117911756</v>
       </c>
       <c r="B75" t="n">
-        <v>97764</v>
+        <v>97771</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>

--- a/artfynd/A 31018-2023 artfynd.xlsx
+++ b/artfynd/A 31018-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9790,6 +9790,132 @@
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>124029731</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57644</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Tallberget, Tallberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>614367</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6661081</v>
+      </c>
+      <c r="S76" t="n">
+        <v>12</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Huddunge</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31018-2023 artfynd.xlsx
+++ b/artfynd/A 31018-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>70118488</v>
+        <v>113206858</v>
       </c>
       <c r="B2" t="n">
-        <v>97919</v>
+        <v>91680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>800 m SO om Björka, vid vägen mot Råksjön, Upl</t>
+          <t>Tallberget, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614330</v>
+        <v>614317</v>
       </c>
       <c r="R2" t="n">
-        <v>6661041</v>
+        <v>6660929</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +750,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2001-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,35 +776,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>fuktig-våt barrskog kring skogsdike</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lennart Karlén</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>70119162</v>
+        <v>113206884</v>
       </c>
       <c r="B3" t="n">
-        <v>98974</v>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,33 +803,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223597</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>800 m SO om Björka, vid vägen mot Råksjön, Upl</t>
+          <t>Tallberget, Tallberget, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614330</v>
+        <v>614314</v>
       </c>
       <c r="R3" t="n">
-        <v>6661041</v>
+        <v>6660902</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,17 +858,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2001-12-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,79 +884,78 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>fuktig-våt barrskog kring skogsdike</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lennart Karlén</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113191941</v>
+        <v>124029731</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tallberget, Upl</t>
+          <t>Tallberget, Tallberget, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614287</v>
+        <v>614367</v>
       </c>
       <c r="R4" t="n">
-        <v>6660925</v>
+        <v>6661081</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,22 +979,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,75 +1009,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113189731</v>
+        <v>70118776</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98219</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>219815</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brändan, Upl</t>
+          <t>800 m SO om Björka, vid vägen mot Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614044</v>
+        <v>614330</v>
       </c>
       <c r="R5" t="n">
-        <v>6660912</v>
+        <v>6661041</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,27 +1086,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:01</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:01</t>
+          <t>2001-12-31</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Inom snitslad yta, ca 10 m från snitslingen.</t>
+          <t>Upplandsfloran - detaljuppgifter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,31 +1107,35 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>fuktig-våt barrskog kring skogsdike</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Lennart Karlén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113192386</v>
+        <v>113189731</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,7 +1160,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1174,13 +1177,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>614189</v>
+        <v>614044</v>
       </c>
       <c r="R6" t="n">
-        <v>6660990</v>
+        <v>6660912</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1219,7 +1222,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Inom snitslad yta, ca 10 m från snitslingen.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,15 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113190699</v>
+        <v>113189787</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,7 +1282,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1287,13 +1299,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>614165</v>
+        <v>614037</v>
       </c>
       <c r="R7" t="n">
-        <v>6660939</v>
+        <v>6660884</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,15 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113190187</v>
+        <v>113190160</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1401,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1409,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>614078</v>
+        <v>614067</v>
       </c>
       <c r="R8" t="n">
-        <v>6660899</v>
+        <v>6660905</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,15 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113190668</v>
+        <v>113190187</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>614138</v>
+        <v>614078</v>
       </c>
       <c r="R9" t="n">
-        <v>6660949</v>
+        <v>6660899</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1576,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,40 +1605,44 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113190532</v>
+        <v>113190458</v>
       </c>
       <c r="B10" t="n">
-        <v>96613</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1644,10 +1650,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>614147</v>
+        <v>614100</v>
       </c>
       <c r="R10" t="n">
-        <v>6660932</v>
+        <v>6660944</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1679,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,40 +1722,44 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113192275</v>
+        <v>113190584</v>
       </c>
       <c r="B11" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1757,10 +1767,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>614173</v>
+        <v>614138</v>
       </c>
       <c r="R11" t="n">
-        <v>6660972</v>
+        <v>6660949</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,7 +1802,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1802,7 +1812,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,15 +1839,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113191042</v>
+        <v>113190599</v>
       </c>
       <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1867,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1870,10 +1884,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>614235</v>
+        <v>614134</v>
       </c>
       <c r="R12" t="n">
-        <v>6660949</v>
+        <v>6660967</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1905,7 +1919,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1929,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,15 +1956,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113190599</v>
+        <v>113190699</v>
       </c>
       <c r="B13" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,16 +1984,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1992,13 +1992,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>614134</v>
+        <v>614165</v>
       </c>
       <c r="R13" t="n">
-        <v>6660967</v>
+        <v>6660939</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,15 +2064,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113190160</v>
+        <v>113191042</v>
       </c>
       <c r="B14" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2097,16 +2092,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2114,13 +2100,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>614067</v>
+        <v>614235</v>
       </c>
       <c r="R14" t="n">
-        <v>6660905</v>
+        <v>6660949</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2149,7 +2135,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2159,7 +2145,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2186,15 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113190458</v>
+        <v>113191224</v>
       </c>
       <c r="B15" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,14 +2213,14 @@
       <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Brändan, Upl</t>
+          <t>Tallberget, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>614100</v>
+        <v>614232</v>
       </c>
       <c r="R15" t="n">
-        <v>6660944</v>
+        <v>6660891</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2271,7 +2252,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2281,7 +2262,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2308,15 +2289,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113192059</v>
+        <v>113191885</v>
       </c>
       <c r="B16" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,29 +2317,18 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tallberget, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>614275</v>
+        <v>614303</v>
       </c>
       <c r="R16" t="n">
-        <v>6660951</v>
+        <v>6660921</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2395,7 +2360,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2405,12 +2370,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan, snitslad och hyggesröjt på delar av granunderväxten. Men fortfarande mkt gran kvar och flerskiktad karaktär på skogen.</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2419,7 +2379,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2438,15 +2397,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113191885</v>
+        <v>113191941</v>
       </c>
       <c r="B17" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,10 +2433,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>614303</v>
+        <v>614287</v>
       </c>
       <c r="R17" t="n">
-        <v>6660921</v>
+        <v>6660925</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2514,7 +2468,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2524,7 +2478,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2554,12 +2508,7 @@
         <v>113192012</v>
       </c>
       <c r="B18" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2673,15 +2622,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113203269</v>
+        <v>113192059</v>
       </c>
       <c r="B19" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,32 +2652,30 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Tallberget, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>614381</v>
+        <v>614275</v>
       </c>
       <c r="R19" t="n">
-        <v>6661105</v>
+        <v>6660951</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2757,22 +2699,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan, snitslad och hyggesröjt på delar av granunderväxten. Men fortfarande mkt gran kvar och flerskiktad karaktär på skogen.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2781,33 +2728,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113204278</v>
+        <v>113192313</v>
       </c>
       <c r="B20" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2834,32 +2777,28 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>614660</v>
+        <v>614189</v>
       </c>
       <c r="R20" t="n">
-        <v>6661181</v>
+        <v>6660990</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2883,22 +2822,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2913,27 +2852,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113203279</v>
+        <v>113192403</v>
       </c>
       <c r="B21" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2958,16 +2892,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2975,13 +2900,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>614205</v>
+        <v>614163</v>
       </c>
       <c r="R21" t="n">
-        <v>6661009</v>
+        <v>6661071</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3005,22 +2930,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3047,15 +2972,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113204090</v>
+        <v>113202811</v>
       </c>
       <c r="B22" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3082,7 +3002,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3097,14 +3017,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>614564</v>
+        <v>614305</v>
       </c>
       <c r="R22" t="n">
-        <v>6661173</v>
+        <v>6661142</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3136,7 +3056,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3146,7 +3066,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3173,15 +3093,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113207025</v>
+        <v>113202915</v>
       </c>
       <c r="B23" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3223,14 +3138,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tallberget (Tallberget), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>614329</v>
+        <v>614321</v>
       </c>
       <c r="R23" t="n">
-        <v>6660982</v>
+        <v>6661125</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3262,7 +3177,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3272,7 +3187,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3299,15 +3214,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113204412</v>
+        <v>113202935</v>
       </c>
       <c r="B24" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3334,32 +3244,28 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>614660</v>
+        <v>614198</v>
       </c>
       <c r="R24" t="n">
-        <v>6661149</v>
+        <v>6661041</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3388,7 +3294,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3398,7 +3304,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3413,54 +3319,49 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113203299</v>
+        <v>113203036</v>
       </c>
       <c r="B25" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3468,21 +3369,17 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Brändan, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>614205</v>
+        <v>614208</v>
       </c>
       <c r="R25" t="n">
-        <v>6661009</v>
+        <v>6661046</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3514,7 +3411,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3524,7 +3421,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3551,15 +3448,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113204814</v>
+        <v>113203065</v>
       </c>
       <c r="B26" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3586,7 +3478,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3601,17 +3493,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>614600</v>
+        <v>614369</v>
       </c>
       <c r="R26" t="n">
-        <v>6661044</v>
+        <v>6661139</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3640,7 +3532,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3650,7 +3542,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3677,15 +3569,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113203036</v>
+        <v>113203266</v>
       </c>
       <c r="B27" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3710,16 +3597,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3727,10 +3605,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>614208</v>
+        <v>614209</v>
       </c>
       <c r="R27" t="n">
-        <v>6661046</v>
+        <v>6661033</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3762,7 +3640,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3772,7 +3650,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3799,15 +3677,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113204335</v>
+        <v>113203269</v>
       </c>
       <c r="B28" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3834,7 +3707,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3849,14 +3722,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>614667</v>
+        <v>614381</v>
       </c>
       <c r="R28" t="n">
-        <v>6661171</v>
+        <v>6661105</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3888,7 +3761,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3898,7 +3771,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3925,15 +3798,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113204128</v>
+        <v>113203279</v>
       </c>
       <c r="B29" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3960,32 +3828,28 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>614592</v>
+        <v>614205</v>
       </c>
       <c r="R29" t="n">
-        <v>6661189</v>
+        <v>6661009</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4014,7 +3878,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4024,7 +3888,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4039,27 +3903,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113203352</v>
+        <v>113203284</v>
       </c>
       <c r="B30" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4086,7 +3945,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4101,17 +3960,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>614431</v>
+        <v>614378</v>
       </c>
       <c r="R30" t="n">
-        <v>6661131</v>
+        <v>6661096</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4140,7 +3999,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4150,7 +4009,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4177,15 +4036,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113202935</v>
+        <v>113203352</v>
       </c>
       <c r="B31" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4212,28 +4066,32 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brändan, Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>614198</v>
+        <v>614431</v>
       </c>
       <c r="R31" t="n">
-        <v>6661041</v>
+        <v>6661131</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4262,7 +4120,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4272,7 +4130,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4287,27 +4145,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113204002</v>
+        <v>113203423</v>
       </c>
       <c r="B32" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4334,7 +4187,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4349,14 +4202,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>614538</v>
+        <v>614449</v>
       </c>
       <c r="R32" t="n">
-        <v>6661174</v>
+        <v>6661155</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4388,7 +4241,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4398,7 +4251,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4425,15 +4278,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113203834</v>
+        <v>113203437</v>
       </c>
       <c r="B33" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4460,7 +4308,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4475,17 +4323,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>614515</v>
+        <v>614455</v>
       </c>
       <c r="R33" t="n">
-        <v>6661196</v>
+        <v>6661157</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4514,7 +4362,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4524,7 +4372,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4551,15 +4399,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113207112</v>
+        <v>113203532</v>
       </c>
       <c r="B34" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4586,7 +4429,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4601,17 +4444,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>614360</v>
+        <v>614468</v>
       </c>
       <c r="R34" t="n">
-        <v>6661036</v>
+        <v>6661157</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4640,7 +4483,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4650,7 +4493,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4677,15 +4520,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113204586</v>
+        <v>113203569</v>
       </c>
       <c r="B35" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4712,7 +4550,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4727,14 +4565,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>614634</v>
+        <v>614485</v>
       </c>
       <c r="R35" t="n">
-        <v>6661058</v>
+        <v>6661170</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4766,7 +4604,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4776,7 +4614,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4803,15 +4641,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113203284</v>
+        <v>113203619</v>
       </c>
       <c r="B36" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4838,7 +4671,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4853,17 +4686,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>614378</v>
+        <v>614480</v>
       </c>
       <c r="R36" t="n">
-        <v>6661096</v>
+        <v>6661194</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4892,7 +4725,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4902,7 +4735,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4929,15 +4762,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113204918</v>
+        <v>113203738</v>
       </c>
       <c r="B37" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4964,7 +4792,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4979,17 +4807,17 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>614572</v>
+        <v>614510</v>
       </c>
       <c r="R37" t="n">
-        <v>6661046</v>
+        <v>6661246</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5018,7 +4846,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5028,7 +4856,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5055,15 +4883,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113205465</v>
+        <v>113203754</v>
       </c>
       <c r="B38" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5090,7 +4913,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5105,14 +4928,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>614427</v>
+        <v>614497</v>
       </c>
       <c r="R38" t="n">
-        <v>6661058</v>
+        <v>6661223</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5144,7 +4967,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5154,7 +4977,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5181,15 +5004,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113205531</v>
+        <v>113203834</v>
       </c>
       <c r="B39" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5216,7 +5034,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5231,17 +5049,17 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>614416</v>
+        <v>614515</v>
       </c>
       <c r="R39" t="n">
-        <v>6661047</v>
+        <v>6661196</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5270,7 +5088,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5280,7 +5098,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5307,15 +5125,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113205738</v>
+        <v>113203906</v>
       </c>
       <c r="B40" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5342,7 +5155,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5357,14 +5170,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>614397</v>
+        <v>614502</v>
       </c>
       <c r="R40" t="n">
-        <v>6661001</v>
+        <v>6661160</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5396,7 +5209,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5406,7 +5219,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5433,15 +5246,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113206984</v>
+        <v>113203943</v>
       </c>
       <c r="B41" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5468,7 +5276,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5483,17 +5291,17 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tallberget (Tallberget), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>614303</v>
+        <v>614528</v>
       </c>
       <c r="R41" t="n">
-        <v>6660953</v>
+        <v>6661149</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5522,7 +5330,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5532,7 +5340,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5559,15 +5367,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113202915</v>
+        <v>113204002</v>
       </c>
       <c r="B42" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5594,7 +5397,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5609,14 +5412,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>614321</v>
+        <v>614538</v>
       </c>
       <c r="R42" t="n">
-        <v>6661125</v>
+        <v>6661174</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5648,7 +5451,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5658,7 +5461,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5685,15 +5488,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113204253</v>
+        <v>113204090</v>
       </c>
       <c r="B43" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5720,7 +5518,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5735,17 +5533,17 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>614632</v>
+        <v>614564</v>
       </c>
       <c r="R43" t="n">
-        <v>6661195</v>
+        <v>6661173</v>
       </c>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5774,7 +5572,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5784,7 +5582,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5811,15 +5609,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113203943</v>
+        <v>113204128</v>
       </c>
       <c r="B44" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5846,7 +5639,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5861,17 +5654,17 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>614528</v>
+        <v>614592</v>
       </c>
       <c r="R44" t="n">
-        <v>6661149</v>
+        <v>6661189</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5900,7 +5693,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5910,7 +5703,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5937,15 +5730,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113204149</v>
+        <v>113204135</v>
       </c>
       <c r="B45" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5972,32 +5760,28 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>614610</v>
+        <v>614116</v>
       </c>
       <c r="R45" t="n">
-        <v>6661181</v>
+        <v>6660992</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6026,7 +5810,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6036,7 +5820,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6051,27 +5835,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113203065</v>
+        <v>113204149</v>
       </c>
       <c r="B46" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6098,7 +5877,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6113,14 +5892,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>614369</v>
+        <v>614610</v>
       </c>
       <c r="R46" t="n">
-        <v>6661139</v>
+        <v>6661181</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6152,7 +5931,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6162,7 +5941,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6189,15 +5968,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113205140</v>
+        <v>113204241</v>
       </c>
       <c r="B47" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6224,7 +5998,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6239,14 +6013,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>614545</v>
+        <v>614633</v>
       </c>
       <c r="R47" t="n">
-        <v>6661121</v>
+        <v>6661183</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6278,7 +6052,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6288,7 +6062,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6315,54 +6089,58 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113206884</v>
+        <v>113204251</v>
       </c>
       <c r="B48" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tallberget (Tallberget), Upl</t>
+          <t>Brändan, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>614314</v>
+        <v>614061</v>
       </c>
       <c r="R48" t="n">
-        <v>6660902</v>
+        <v>6661042</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6391,7 +6169,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6401,7 +6179,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6416,27 +6194,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113206047</v>
+        <v>113204253</v>
       </c>
       <c r="B49" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6463,7 +6236,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6478,17 +6251,17 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Tallberget (Tallberget), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>614357</v>
+        <v>614632</v>
       </c>
       <c r="R49" t="n">
-        <v>6660963</v>
+        <v>6661195</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6517,7 +6290,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6527,7 +6300,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6554,15 +6327,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113203906</v>
+        <v>113204278</v>
       </c>
       <c r="B50" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6589,7 +6357,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6604,17 +6372,17 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>614502</v>
+        <v>614660</v>
       </c>
       <c r="R50" t="n">
-        <v>6661160</v>
+        <v>6661181</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6643,7 +6411,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6653,7 +6421,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6680,15 +6448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113203569</v>
+        <v>113204335</v>
       </c>
       <c r="B51" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6715,7 +6478,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6730,14 +6493,14 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>614485</v>
+        <v>614667</v>
       </c>
       <c r="R51" t="n">
-        <v>6661170</v>
+        <v>6661171</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6769,7 +6532,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6779,7 +6542,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6806,15 +6569,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113203437</v>
+        <v>113204412</v>
       </c>
       <c r="B52" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6841,7 +6599,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6856,14 +6614,14 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>614455</v>
+        <v>614660</v>
       </c>
       <c r="R52" t="n">
-        <v>6661157</v>
+        <v>6661149</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6895,7 +6653,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6905,7 +6663,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6932,15 +6690,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>113206861</v>
+        <v>113204506</v>
       </c>
       <c r="B53" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6967,7 +6720,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6982,14 +6735,14 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Tallberget (Tallberget), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>614300</v>
+        <v>614670</v>
       </c>
       <c r="R53" t="n">
-        <v>6660916</v>
+        <v>6661060</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -7021,7 +6774,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7031,7 +6784,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7058,15 +6811,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>113203266</v>
+        <v>113204586</v>
       </c>
       <c r="B54" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7091,21 +6839,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Brändan, Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>614209</v>
+        <v>614634</v>
       </c>
       <c r="R54" t="n">
-        <v>6661033</v>
+        <v>6661058</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7134,7 +6895,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7144,7 +6905,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7159,27 +6920,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>113203423</v>
+        <v>113204814</v>
       </c>
       <c r="B55" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7206,7 +6962,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7221,17 +6977,17 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>614449</v>
+        <v>614600</v>
       </c>
       <c r="R55" t="n">
-        <v>6661155</v>
+        <v>6661044</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7260,7 +7016,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7270,7 +7026,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7297,15 +7053,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>113205106</v>
+        <v>113204918</v>
       </c>
       <c r="B56" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7332,7 +7083,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7347,17 +7098,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>614557</v>
+        <v>614572</v>
       </c>
       <c r="R56" t="n">
-        <v>6661101</v>
+        <v>6661046</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7386,7 +7137,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7396,7 +7147,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7423,15 +7174,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>113204241</v>
+        <v>113205106</v>
       </c>
       <c r="B57" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7458,7 +7204,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7473,14 +7219,14 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>614633</v>
+        <v>614557</v>
       </c>
       <c r="R57" t="n">
-        <v>6661183</v>
+        <v>6661101</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7512,7 +7258,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7522,7 +7268,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7549,15 +7295,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>113203619</v>
+        <v>113205140</v>
       </c>
       <c r="B58" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7584,7 +7325,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7599,17 +7340,17 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>614480</v>
+        <v>614545</v>
       </c>
       <c r="R58" t="n">
-        <v>6661194</v>
+        <v>6661121</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7638,7 +7379,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7648,7 +7389,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7675,15 +7416,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>113205219</v>
+        <v>113205160</v>
       </c>
       <c r="B59" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7710,7 +7446,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7725,17 +7461,17 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>614508</v>
+        <v>614533</v>
       </c>
       <c r="R59" t="n">
-        <v>6661094</v>
+        <v>6661101</v>
       </c>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7764,7 +7500,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7774,7 +7510,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7801,15 +7537,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>113206946</v>
+        <v>113205219</v>
       </c>
       <c r="B60" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7836,28 +7567,32 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Tallberget, Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>614300</v>
+        <v>614508</v>
       </c>
       <c r="R60" t="n">
-        <v>6660950</v>
+        <v>6661094</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7886,7 +7621,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7896,7 +7631,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7911,49 +7646,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>113206858</v>
+        <v>113205465</v>
       </c>
       <c r="B61" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7963,23 +7693,27 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Tallberget, Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>614317</v>
+        <v>614427</v>
       </c>
       <c r="R61" t="n">
-        <v>6660929</v>
+        <v>6661058</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8008,7 +7742,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8018,7 +7752,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8033,27 +7767,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>113205160</v>
+        <v>113205531</v>
       </c>
       <c r="B62" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8080,7 +7809,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -8095,17 +7824,17 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>614533</v>
+        <v>614416</v>
       </c>
       <c r="R62" t="n">
-        <v>6661101</v>
+        <v>6661047</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8134,7 +7863,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8144,7 +7873,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8171,15 +7900,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>113204506</v>
+        <v>113205606</v>
       </c>
       <c r="B63" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8206,7 +7930,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8221,17 +7945,17 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>614670</v>
+        <v>614401</v>
       </c>
       <c r="R63" t="n">
-        <v>6661060</v>
+        <v>6661019</v>
       </c>
       <c r="S63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8260,7 +7984,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8270,7 +7994,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8297,15 +8021,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>113203738</v>
+        <v>113205738</v>
       </c>
       <c r="B64" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8332,7 +8051,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -8347,17 +8066,17 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>614510</v>
+        <v>614397</v>
       </c>
       <c r="R64" t="n">
-        <v>6661246</v>
+        <v>6661001</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8386,7 +8105,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8396,7 +8115,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8423,15 +8142,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>113207101</v>
+        <v>113206047</v>
       </c>
       <c r="B65" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8458,28 +8172,32 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Tallberget, Upl</t>
+          <t>Tallberget, Tallberget, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>614342</v>
+        <v>614357</v>
       </c>
       <c r="R65" t="n">
-        <v>6661025</v>
+        <v>6660963</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8508,7 +8226,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8518,7 +8236,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8533,27 +8251,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>113207023</v>
+        <v>113206218</v>
       </c>
       <c r="B66" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8580,28 +8293,32 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Tallberget, Upl</t>
+          <t>Tallberget, Tallberget, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>614314</v>
+        <v>614357</v>
       </c>
       <c r="R66" t="n">
-        <v>6660969</v>
+        <v>6660930</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8630,7 +8347,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8640,7 +8357,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8655,27 +8372,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>113203532</v>
+        <v>113206861</v>
       </c>
       <c r="B67" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8702,7 +8414,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8717,17 +8429,17 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Tallberget, Tallberget, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>614468</v>
+        <v>614300</v>
       </c>
       <c r="R67" t="n">
-        <v>6661157</v>
+        <v>6660916</v>
       </c>
       <c r="S67" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8756,7 +8468,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8766,7 +8478,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8793,15 +8505,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>113205606</v>
+        <v>113206946</v>
       </c>
       <c r="B68" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8828,32 +8535,28 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Tallberget, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>614401</v>
+        <v>614300</v>
       </c>
       <c r="R68" t="n">
-        <v>6661019</v>
+        <v>6660950</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8882,7 +8585,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8892,7 +8595,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8907,27 +8610,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>113203754</v>
+        <v>113206984</v>
       </c>
       <c r="B69" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8954,7 +8652,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8969,14 +8667,14 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Brändan (Brändan), Upl</t>
+          <t>Tallberget, Tallberget, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>614497</v>
+        <v>614303</v>
       </c>
       <c r="R69" t="n">
-        <v>6661223</v>
+        <v>6660953</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -9008,7 +8706,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9018,7 +8716,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9045,15 +8743,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>113216624</v>
+        <v>113207023</v>
       </c>
       <c r="B70" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9080,26 +8773,28 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>NV om Råksjön, Upl</t>
+          <t>Tallberget, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>614187</v>
+        <v>614314</v>
       </c>
       <c r="R70" t="n">
-        <v>6661055</v>
+        <v>6660969</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9128,7 +8823,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9138,12 +8833,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Mycket fin skog med gamla träd. Nyligen röjd.</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9152,34 +8842,28 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>113216693</v>
+        <v>113207025</v>
       </c>
       <c r="B71" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9206,26 +8890,32 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>NV om Råksjön, Upl</t>
+          <t>Tallberget, Tallberget, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>614304</v>
+        <v>614329</v>
       </c>
       <c r="R71" t="n">
-        <v>6660949</v>
+        <v>6660982</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9254,7 +8944,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9264,7 +8954,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9273,34 +8963,28 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>113216694</v>
+        <v>113207101</v>
       </c>
       <c r="B72" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9327,26 +9011,28 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>NV om Råksjön, Upl</t>
+          <t>Tallberget, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>614318</v>
+        <v>614342</v>
       </c>
       <c r="R72" t="n">
-        <v>6660989</v>
+        <v>6661025</v>
       </c>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9375,7 +9061,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9385,7 +9071,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9394,34 +9080,28 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>113216645</v>
+        <v>113207112</v>
       </c>
       <c r="B73" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9448,26 +9128,32 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>NV om Råksjön, Upl</t>
+          <t>Brändan, Brändan, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>614272</v>
+        <v>614360</v>
       </c>
       <c r="R73" t="n">
-        <v>6660956</v>
+        <v>6661036</v>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9496,7 +9182,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9506,7 +9192,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9515,34 +9201,28 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>113216634</v>
+        <v>113216624</v>
       </c>
       <c r="B74" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9569,7 +9249,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J74" t="inlineStr"/>
@@ -9582,13 +9262,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>614186</v>
+        <v>614187</v>
       </c>
       <c r="R74" t="n">
-        <v>6660973</v>
+        <v>6661055</v>
       </c>
       <c r="S74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9617,7 +9297,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9627,7 +9307,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Mycket fin skog med gamla träd. Nyligen röjd.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9655,57 +9340,56 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117911756</v>
+        <v>113216634</v>
       </c>
       <c r="B75" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Råksjön, väst om, Tärnsjö-Gräsbo, Upl</t>
+          <t>NV om Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>614079</v>
+        <v>614186</v>
       </c>
       <c r="R75" t="n">
-        <v>6661024</v>
+        <v>6660973</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9729,12 +9413,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9750,79 +9444,68 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124029731</v>
+        <v>113216645</v>
       </c>
       <c r="B76" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Tallberget, Tallberget, Upl</t>
+          <t>NV om Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>614367</v>
+        <v>614272</v>
       </c>
       <c r="R76" t="n">
-        <v>6661081</v>
+        <v>6660956</v>
       </c>
       <c r="S76" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9846,22 +9529,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2023-11-12</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2023-11-12</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9870,21 +9553,1695 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
+          <t>Eric Grund</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Eric Grund</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>113216693</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>NV om Råksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>614304</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6660949</v>
+      </c>
+      <c r="S77" t="n">
+        <v>1</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Huddunge</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Eric Grund</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Eric Grund</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>113216694</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>NV om Råksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>614318</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6660989</v>
+      </c>
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Huddunge</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Eric Grund</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Eric Grund</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>124033534</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Tallberget, Tallberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>614615</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6661217</v>
+      </c>
+      <c r="S79" t="n">
+        <v>4</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Huddunge</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
           <t>Emil V. Nilsson</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
+      <c r="AX79" t="inlineStr">
         <is>
           <t>Emil V. Nilsson</t>
         </is>
       </c>
-      <c r="AY76" t="inlineStr"/>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>113186658</v>
+      </c>
+      <c r="B80" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Brändan, Upl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>614163</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6661071</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Huddunge</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>113192275</v>
+      </c>
+      <c r="B81" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Brändan, Upl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>614173</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6660972</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Huddunge</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>113203299</v>
+      </c>
+      <c r="B82" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Brändan, Upl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>614205</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6661009</v>
+      </c>
+      <c r="S82" t="n">
+        <v>15</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Huddunge</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>70118488</v>
+      </c>
+      <c r="B83" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>800 m SO om Björka, vid vägen mot Råksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>614330</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6661041</v>
+      </c>
+      <c r="S83" t="n">
+        <v>100</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Huddunge</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2001-01-01</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2001-12-31</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>fuktig-våt barrskog kring skogsdike</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Lennart Karlén</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>113190532</v>
+      </c>
+      <c r="B84" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Brändan, Upl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>614147</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6660932</v>
+      </c>
+      <c r="S84" t="n">
+        <v>15</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Huddunge</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>70117397</v>
+      </c>
+      <c r="B85" t="n">
+        <v>103764</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>222004</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Kärrviol</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>800 m SO om Björka, vid vägen mot Råksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>614330</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6661041</v>
+      </c>
+      <c r="S85" t="n">
+        <v>100</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Huddunge</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2001-01-01</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2001-12-31</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>fuktig-våt barrskog kring skogsdike</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Lennart Karlén</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>70119601</v>
+      </c>
+      <c r="B86" t="n">
+        <v>98277</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>222736</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Majbräken</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Athyrium filix-femina</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>800 m SO om Björka, vid vägen mot Råksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>614330</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6661041</v>
+      </c>
+      <c r="S86" t="n">
+        <v>100</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Huddunge</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2001-01-01</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2001-12-31</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>fuktig-våt barrskog kring skogsdike</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Lennart Karlén</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>70119675</v>
+      </c>
+      <c r="B87" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>800 m SO om Björka, vid vägen mot Råksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>614330</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6661041</v>
+      </c>
+      <c r="S87" t="n">
+        <v>100</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Huddunge</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2001-01-01</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2001-12-31</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>fuktig-våt barrskog kring skogsdike</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Lennart Karlén</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>70119208</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>800 m SO om Björka, vid vägen mot Råksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>614330</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6661041</v>
+      </c>
+      <c r="S88" t="n">
+        <v>100</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Huddunge</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2001-01-01</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2001-12-31</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>friska-fuktiga vägkanter vid grusväg genom barrskog</t>
+        </is>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Lennart Karlén</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>70118812</v>
+      </c>
+      <c r="B89" t="n">
+        <v>102871</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>223037</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Humleblomster</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Geum rivale</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>800 m SO om Björka, vid vägen mot Råksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>614330</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6661041</v>
+      </c>
+      <c r="S89" t="n">
+        <v>100</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Huddunge</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2001-01-01</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2001-12-31</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>fuktig-våt barrskog kring skogsdike</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Lennart Karlén</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>117911756</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Råksjön, väst om, Tärnsjö-Gräsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>614079</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6661024</v>
+      </c>
+      <c r="S90" t="n">
+        <v>25</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Huddunge</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>70119162</v>
+      </c>
+      <c r="B91" t="n">
+        <v>99115</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>800 m SO om Björka, vid vägen mot Råksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>614330</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6661041</v>
+      </c>
+      <c r="S91" t="n">
+        <v>100</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Huddunge</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2001-01-01</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2001-12-31</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>fuktig-våt barrskog kring skogsdike</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Lennart Karlén</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31018-2023 artfynd.xlsx
+++ b/artfynd/A 31018-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY91"/>
+  <dimension ref="A1:AZ91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113206858</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113206884</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124029731</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70118776</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1251,6 +1276,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113189731</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113189787</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1485,6 +1520,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113190160</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1602,6 +1642,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113190187</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1719,6 +1764,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113190458</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1836,6 +1886,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113190584</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1953,6 +2008,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113190599</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2061,6 +2121,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113190699</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2169,6 +2234,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113191042</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2286,6 +2356,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113191224</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2394,6 +2469,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113191885</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2502,6 +2582,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113191941</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2619,6 +2704,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113192012</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2744,6 +2834,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113192059</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2861,6 +2956,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113192313</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2969,6 +3069,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113192403</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3090,6 +3195,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113202811</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3211,6 +3321,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113202915</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3328,6 +3443,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113202935</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3445,6 +3565,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203036</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3566,6 +3691,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203065</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3674,6 +3804,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203266</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3795,6 +3930,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203269</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3912,6 +4052,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203279</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4033,6 +4178,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203284</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4154,6 +4304,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203352</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4275,6 +4430,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203423</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4396,6 +4556,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203437</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4517,6 +4682,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203532</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4638,6 +4808,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203569</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4759,6 +4934,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203619</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4880,6 +5060,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203738</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5001,6 +5186,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203754</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5122,6 +5312,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203834</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5243,6 +5438,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203906</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5364,6 +5564,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203943</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5485,6 +5690,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113204002</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5606,6 +5816,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113204090</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5727,6 +5942,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113204128</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5844,6 +6064,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113204135</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5965,6 +6190,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113204149</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6086,6 +6316,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113204241</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6203,6 +6438,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113204251</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6324,6 +6564,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113204253</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6445,6 +6690,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113204278</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6566,6 +6816,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113204335</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6687,6 +6942,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113204412</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6808,6 +7068,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113204506</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6929,6 +7194,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113204586</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7050,6 +7320,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113204814</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7171,6 +7446,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113204918</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7292,6 +7572,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113205106</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7413,6 +7698,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113205140</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7534,6 +7824,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113205160</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7655,6 +7950,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113205219</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7776,6 +8076,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113205465</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7897,6 +8202,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113205531</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8018,6 +8328,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113205606</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8139,6 +8454,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113205738</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8260,6 +8580,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113206047</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8381,6 +8706,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113206218</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8502,6 +8832,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113206861</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8619,6 +8954,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113206946</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8740,6 +9080,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113206984</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8857,6 +9202,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113207023</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8978,6 +9328,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113207025</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9095,6 +9450,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113207101</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9216,6 +9576,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113207112</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9337,6 +9702,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113216624</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9453,6 +9823,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113216634</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9569,6 +9944,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113216645</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9685,6 +10065,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113216693</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9801,6 +10186,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113216694</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9922,6 +10312,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124033534</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10030,6 +10425,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113186658</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10138,6 +10538,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113192275</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10259,6 +10664,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113203299</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10370,6 +10780,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70118488</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10478,6 +10893,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113190532</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10589,6 +11009,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70117397</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10700,6 +11125,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70119601</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10811,6 +11241,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70119675</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10922,6 +11357,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70119208</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11031,6 +11471,11 @@
       <c r="AY89" t="inlineStr">
         <is>
           <t>Upplands Flora 2010</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70118812</t>
         </is>
       </c>
     </row>
@@ -11135,6 +11580,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117911756</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11242,8 +11692,105 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70119162</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>